--- a/extenbooks/S901.xlsx
+++ b/extenbooks/S901.xlsx
@@ -1236,10 +1236,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–2024</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -1397,114 +1397,123 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S901-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S901-A/LpL_S511</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S901-A/NSW_V_S608</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S901-A/VW_S512</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S901-A/e_S506</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S901 — Summary Indicators (Chapter 9 Summary Table)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 9 — Marxian National Accounts: Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Source**: composed from S506, S511, S512, S608 final CSVs (with placeholders for S513, S514)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: mixed (ratio / rate / share by column)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>**Period**: 1948-1989 (book), with row-by-row pending markers where K* / TCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>required for S513 / S514</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t># S901 — Summary Indicators (Chapter-9-Style Summary Table)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>**Status**: book_period_validated (partial — pending K* unlocks 88 of 252 cells)</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>## Series</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>- **SID**: S901</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The book's Chapter 9 summary aggregates the headline Marxian magnitudes into a single table so a reader can see all the key ratios side-by-side year-by-year. The new build constructs this purely from already-validated upstream series — no new source data:</t>
+          <t>- **Name**: Summary Indicators (project-internal Chapter-9-style summary table)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>- **Chapter**: 9 (project-internal label). **Important**: the printed book has only seven chapters plus Appendices A-N. There is no Chapter 9 and no Table 9.1 in the book. The in-book analog is Ch7 §§7.1-7.5 ("Summary and conclusions"). S901 is a project-internal aggregation that mirrors what a printed summary table would have contained.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>- `S506` exploitation rate `e = S*/V*`</t>
+          <t>- **Status**: `book_period_validated` (1948-1989; extension blocked until upstream extensions complete)</t>
         </is>
       </c>
     </row>
@@ -1512,39 +1521,31 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>- `S511` productive labor share `Lp/L`</t>
+          <t>- **Units**: mixed long-format (ratio / rate / share by column)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>- `S512` productive wage share `V*/W`</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>- `S513` Marxian profit rate `r* = S*/(C*+V*)`  — **pending K\* (Wave 3 follow-up)**</t>
+          <t>## Methodology</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>- `S514` capacity-adjusted profit rate `r*_adj = r*·TCU`  — **pending K\* and TCU**</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>- `S608` NSW/V* ratio (from Wave 2)</t>
+          <t>S901 is a purely derived composite table assembling key Marxian indicators from Ch5 (production accounts) and Ch6 (distribution accounts) into a single long-format summary. No independent NIPA inputs are required. The P02 processor reads each upstream `data/final/&lt;sid&gt;.csv`, projects the `&lt;sid&gt;-A` (book-period) subseries, and emits one long-format row per `(year, indicator)` pair. The six indicators are: `S506` (exploitation rate `e = S*/V*`), `S511` (productive labor share `Lp/L`), `S512` (productive wage share `V*/W`), `S513` (Marxian profit rate `r* = S*/(C*+V*)` — pending K* sourcing), `S514` (capacity-adjusted profit rate `r*_adj = r* · TCU` — pending K* and TCU), and `S608` (NSW/V* ratio from Wave 2). Pending indicators are explicit NaN, not synthesized values.</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1557,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>The substantive content S901 is meant to display is the book's headline empirical contrast between Marxian and orthodox magnitudes. The verbatim summary anchor is **"Marxian total product TP* is roughly 82% of the IO measure of gross product GP, but about 1.5 times larger than the conventional measure of GNP. Marxian gross final product GFP*, on the other hand, is about 15% smaller than GNP (Table 5.4). Surplus value S* is almost double the most inclusive measure of profit-type income P+ (defined as NNP minus employee compensation), while productive labor L_p is less than one-half of all employment L. As a result, the rate of surplus value S*/V* is typically almost four times as large as the ratio of profit-type income to employee compensation P+/EC, while the Marxian measure of productivity q* (defined as real total product per productive labor hour) is about 3 times as large as the conventional measure (defined as real GDP per labor hour) (Section 5.12, Table 5.14)."** (ST 1994 Ch7 §7.3, p.221). The two-phase profit-rate narrative the table is meant to surface is **"From 1948 to 1980, the rate of surplus value rises modestly by roughly 22%, while the adjusted value composition rises by over 77% (and the adjusted materialized composition C*K/(V*+S*) rises by over 56%). The rising value composition overwhelms the rising rate of surplus value, so that the adjusted Marxian rate of profit falls by almost a third over this period. This is striking empirical support for Marx's theory of the falling rate of profit."** (ST 1994 Ch7 §7.1, p.214); and **"The second period, from 1980 to 1989, spans the Reagan-Bush era … The rise in the rate of surplus value accelerates in this period, more than doubling its trend rate. Moreover, the growth in the value and materialized compositions decelerate in this period … The overall effect is to modestly reverse the fall in the general rate of profit, recovering about 8% of its initial value."** (ST 1994 Ch7 §7.1, p.214).</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1569,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Purely aggregative. The P02 processor reads each upstream `data/final/{sid}.csv`, projects the `{sid}-A` subseries, and emits one long-format row per (year, indicator) pair. Pending indicators are explicit NaN (not synthesized).</t>
+          <t>V03 validation is purely a round-trip: for every populated `(year, indicator)` cell, the value must equal the corresponding cell in the upstream final CSV at the matching year with `abs_err &lt; 1e-9`. Current PASS rate: 164/164 populated pairs across 4 columns × 41 years. The remaining 88 cells (S513 + S514 columns × all years) are NaN by design — they activate when K* (productive fixed-capital stock) and TCU (capacity utilization) are sourced. The project's no-synthetic-data rule is the explicit reason these cells remain NaN rather than carrying placeholder values. S901's reason-for-existing is captured in the book's own self-description of its purpose: **"The whole purpose of this book has been to show that the middle road is truly different, both theoretically and empirically."** (ST 1994 Ch7 §7.2, p.220).</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1581,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>## Validation</t>
+          <t>## Sources</t>
         </is>
       </c>
     </row>
@@ -1592,31 +1593,39 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>V03 round-trips: for every populated cell, S901 = upstream final/X.csv at the matching year, abs_err &lt; 1e-9. PASS at 164/164 populated pairs across 4 columns × 41 years.</t>
+          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_24/full_transcription.md` (Ch7 §7.1 — Phase-1 1948-1980 narrative, Figure 7.1 social-burden rate, Figure 7.2 NIPA-vs-Marxian rate); `chunk_25/full_transcription.md` (Ch7 §7.3 — Lp &lt; 0.5L, S*/V* approximately 4× P+/EC, value composition rising 90%); `Knowledge_Base/tables/page_140_marxian_orthodox_comparison.csv` (Table 5.14 comparison ratios — TP*/GP=82%, TP*/GNP=147%, S*/P=224%, S*/V*=210% of orthodox equivalents); `Knowledge_Base/SUMMARY_KEY_FINDINGS.md`; `Technical/docs/chapters/CHAPTER_9_INVESTIGATION.md`; `Knowledge_Base/text/narrative_chunk_{15,16,17}_ch5.md`; `Knowledge_Base/text/narrative_chunk_{18,20}_ch6.md`</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>- Book tables: Table 5.14 (Marxian vs orthodox comparison ratios, p.140); Figures 7.1 / 7.2 (in-book equivalents of "Chapter 9 figures"); the book has no actual Table 9.1</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>## Coverage gap</t>
+          <t>- External sources: none — S901 is purely aggregative</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>- Upstream series: S506, S511, S512, S513 (pending K*), S514 (pending K* and TCU), S608</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>88 cells (S513 + S514 columns × all years) are NaN. They activate when K* is sourced. The DPR explicitly does NOT carry guessed values — the no-synthetic-data rule.</t>
+          <t>- Local files: each upstream's `data/final/&lt;sid&gt;.csv`</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1637,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>## Reference values</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1649,239 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
+          <t>- 41 book-period years 1948-1989; 164/164 populated `(year, indicator)` cells pass round-trip with `abs_err &lt; 1e-9`</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>- Headline 1948-1989 book values (drawn from Ch7 §7.3 p.221 and the project's Wave-1 finals):</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Exploitation rate `e = S*/V*`: 1.70 (1948) → 2.44 (1989), +44%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Productive labor share `Lp/L`: 0.57 (1948) → 0.36 (1989), −37%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Productive wage share `V*/W`: 0.54 (1948) → 0.36 (1989), −33%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Net social wage (NSW): negative throughout the postwar period (workers are net payers to the state, per Ch7 §7.3 p.223 and Appendix N)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>- Marxian-vs-orthodox ratios from Table 5.14 (p.140): TP*/GP = 82%, TP*/GNP = 147%, S*/P = 224%, S*/V* = 210% of conventional equivalents</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>- Marxian profit rate (book aggregate): falls 25% over 1948-1989; NIPA-based net rate r'n falls 39% (faster because of the rising social burden rate b — Figure 7.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>- Coverage gap: 88 cells (S513 + S514 columns × 41 years) are NaN pending K* and TCU; no synthetic fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>## Known issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>- **Book has no Chapter 9 and no Table 9.1**: S901 is a project-internal aggregation. Verified against book TOC pp.v-vii — chapters run 1-7 plus Appendices A-N</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>- Purely derived — inherits all upstream caveats from S506, S511, S512, S513, S514, S608</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>- Extension beyond 1989 blocked until all six upstream series are independently extended (Stage 4 EPRs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>- Table 5.14 comparison ratios are period-specific and may not hold under NAICS reclassification (1997+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>- S513 (Marxian profit rate) requires K* (productive fixed capital stock) — currently uses total K, producing understated levels but correct trend ([internal-decision-record])</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>- S514 requires both K* and TCU (capacity utilization) — neither sourced yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>- VA*/W constant assumption partially resolved in Session 14 ([internal-decision-record]); S506/S512 extension period carries small systematic error from SIC-NAICS gap interpolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>- The CHAPTER_9_INVESTIGATION.md project doc is the load-bearing internal record of why S901 has the columns it does</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>- Upstream: S506 (exploitation rate), S511 (Lp/L), S512 (V*/W), S513 (r*), S514 (r*_adj), S608 (NSW/V*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>- Comparison data: Table 5.14 (page_140_marxian_orthodox_comparison.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>- Downstream: visualization layer (Stage 7); publication summary tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>- Related: S801 (cross-study comparison — same family of "summary view" artifacts); AS001 (social burden rate `b = t + eu` — the mechanism linking S513 to NIPA r'n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/S901_research.json`, researcher `agent`, 2026-03-21; ported from `ST2/research/T901_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 (`D3_RMWND_quotes_ch7_etc`) and 2026-05-23 (`stage1_cohort3_enrich`, `stage1_cohort3_S901AS001AS002`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 24/25 + Knowledge_Base/tables/page_140 + Knowledge_Base/SUMMARY_KEY_FINDINGS + Technical/docs/chapters/CHAPTER_9_INVESTIGATION + registry entry + project CLAUDE.md (which mandates disclosure that S901 is a project artifact beyond the book's 7 chapters)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
         </is>
       </c>
     </row>
@@ -1655,10 +1896,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1683,255 +1924,395 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S901 is a purely derived composite table assembling key indicators from Ch5 and Ch6 into Table 9.1. No independent NIPA inputs are required. Construction proceeds by collecting final values from six upstream series: S506 (rate of exploitation e = S*/V*), S511 (productive labor share Lp/L), S512 (productive wage share V*/W), S513 (Marxian rate of profit r*), S514 (adjusted rate of profit r*_adj), and S608 (net social wage ratio NSW/V*). Subseries S901-A covers the book period 1948-1989.</t>
+          <t>Marxian total product TP* is roughly 82% of the IO measure of gross product GP, but about 1.5 times larger than the conventional measure of GNP. Marxian gross final product GFP*, on the other hand, is about 15% smaller than GNP (Table 5.4). Surplus value S* is almost double the most inclusive measure of profit-type income P+ (defined as NNP minus employee compensation), while productive labor L_p is less than one-half of all employment L. As a result, the rate of surplus value S*/V* is typically almost four times as large as the ratio of profit-type income to employee compensation P+/EC, while the Marxian measure of productivity q* (defined as real total product per productive labor hour) is about 3 times as large as the conventional measure (defined as real GDP per labor hour) (Section 5.12, Table 5.14).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch9; CHAPTER_9_INVESTIGATION.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>key_finding</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rate of exploitation (e = S*/V*) rose from 1.70 to 2.44 over 1948-1989, a 44% increase. Productive labor share (Lp/L) fell from 57% to 36% (-37%). Productive wage share (V*/W) fell from 54% to 36% (-33%). The net social wage (NSW) is negative throughout the entire period, meaning workers are net payers to the state rather than net beneficiaries.</t>
+          <t>From 1948 to 1980, the rate of surplus value rises modestly by roughly 22%, while the adjusted value composition rises by over 77% (and the adjusted materialized composition C*K/(V*+S*) rises by over 56%). The rising value composition overwhelms the rising rate of surplus value, so that the adjusted Marxian rate of profit falls by almost a third over this period. This is striking empirical support for Marx's theory of the falling rate of profit.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST_1994, Ch9 pp.236-240; Knowledge_Base/SUMMARY_KEY_FINDINGS.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>comparison_data</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Table 5.14 (page 140) provides the Marxian-vs-orthodox comparison ratios: TP*/GP = 82%, TP*/GNP = 147%, S*/P = 224%, S*/V* = 210% of conventional equivalents. Marxian productivity grows faster than conventional measures (+49% vs lower orthodox measures). These ratios demonstrate that the theoretical distinction between Marxian and orthodox categories produces fundamentally different empirical magnitudes.</t>
+          <t>The second period, from 1980 to 1989, spans the Reagan-Bush era, during which the capitalist class and the state collaborated in attacking workers' living standards and labor conditions. The rise in the rate of surplus value accelerates in this period, more than doubling its trend rate. Moreover, the growth in the value and materialized compositions decelerate in this period, because the low profit rate and slow accumulation inhibit the adoption of new, more capital-intensive technologies. The overall effect is to modestly reverse the fall in the general rate of profit, recovering about 8% of its initial value.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Table 5.14 p.140; Knowledge_Base/tables/page_140_marxian_orthodox_comparison.csv</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fig 9.1 plots productive vs unproductive consumption over 1948-1989, showing the growing share absorbed by unproductive activities. Fig 9.2 pairs productive consumption with capital stock trends. Fig 9.3 presents rates of productive consumption. Fig 9.4 shows rates of capital accumulation. Fig 9.5 displays rates of surplus value (exploitation) over time, the central empirical result of the book.</t>
+          <t>Figure 7.2 shows that, as a result, the (net of profit taxes) NIPA-based rate of profit r'n falls substantially faster than the Marxian rate: while the Marxian rate falls by 25%, the NIPA-based rate falls by 39%.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch9 Figs 9.1-9.5</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dependency_chain</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S901 depends on six series: S506 (e = S*/V*), S511 (Lp/L), S512 (V*/W), S513 (r*), S514 (r*_adj), S608 (NSW/V*). Additionally, Table 5.14 comparison data is sourced from page_140_marxian_orthodox_comparison.csv. All upstream series must be built and validated before S901 can be assembled. No BEA or other external data feeds are needed — S901 is purely an aggregation layer.</t>
+          <t>For the United States, the taxes paid turn out to be generally larger than the social benefits received -- that is, there is a net tax paid by labor. This implies that true variable capital is somewhat lower, and the true mass and rate of surplus value somewhat higher, than the apparent rates (Section 5.9, Figures 5.23-5.25).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CHAPTER_9_INVESTIGATION.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>key_finding</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The book's central empirical conclusion (p.240): 'The theoretical difference between Marxian and orthodox economic analysis is reflected in a fundamentally different empirical picture of capitalist reality.' The summary table quantifies this divergence across every major aggregate — output, wages, profit, exploitation, and accumulation.</t>
+          <t>S901 is a purely derived composite table assembling key indicators from Ch5 and Ch6 into Table 9.1. No independent NIPA inputs are required. Construction proceeds by collecting final values from six upstream series: S506 (rate of exploitation e = S*/V*), S511 (productive labor share Lp/L), S512 (productive wage share V*/W), S513 (Marxian rate of profit r*), S514 (adjusted rate of profit r*_adj), and S608 (net social wage ratio NSW/V*). Subseries S901-A covers the book period 1948-1989.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ST_1994, p.240</t>
+          <t>ST_1994, Ch9; CHAPTER_9_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>key_finding</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S901 inherits all caveats from its upstream series. Any measurement issues in S506, S511-T514, or S608 propagate directly into the summary table. The comparison ratios from Table 5.14 are point-in-time and may shift under different sector classification regimes (SIC vs NAICS). Extension beyond 1989 requires all six upstream series to be independently extended first.</t>
+          <t>Rate of exploitation (e = S*/V*) rose from 1.70 to 2.44 over 1948-1989, a 44% increase. Productive labor share (Lp/L) fell from 57% to 36% (-37%). Productive wage share (V*/W) fell from 54% to 36% (-33%). The net social wage (NSW) is negative throughout the entire period, meaning workers are net payers to the state rather than net beneficiaries.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CHAPTER_9_INVESTIGATION.md</t>
+          <t>ST_1994, Ch9 pp.236-240; Knowledge_Base/SUMMARY_KEY_FINDINGS.md</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>comparison_data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The summary table serves as the capstone of the book's empirical framework, synthesizing results from the production accounts (Ch5) and distribution accounts (Ch6) into a single view. The Marxian categories — productive labor, variable capital, surplus value — are shown alongside their orthodox counterparts to highlight systematic divergences in level and trend.</t>
+          <t>Table 5.14 (page 140) provides the Marxian-vs-orthodox comparison ratios: TP*/GP = 82%, TP*/GNP = 147%, S*/P = 224%, S*/V* = 210% of conventional equivalents. Marxian productivity grows faster than conventional measures (+49% vs lower orthodox measures). These ratios demonstrate that the theoretical distinction between Marxian and orthodox categories produces fundamentally different empirical magnitudes.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ST_1994, Ch9 pp.236-240; Knowledge_Base/SUMMARY_KEY_FINDINGS.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>ST_1994, Table 5.14 p.140; Knowledge_Base/tables/page_140_marxian_orthodox_comparison.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fig 9.1 plots productive vs unproductive consumption over 1948-1989, showing the growing share absorbed by unproductive activities. Fig 9.2 pairs productive consumption with capital stock trends. Fig 9.3 presents rates of productive consumption. Fig 9.4 shows rates of capital accumulation. Fig 9.5 displays rates of surplus value (exploitation) over time, the central empirical result of the book.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch9 Figs 9.1-9.5</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>dependency_chain</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S901 is a purely derived summary table assembling key Marxian indicators from Ch5 (S506, S511-T514) and Ch6 (S608) into Table 9.1. No independent data inputs. Covers 1948-1989 (subseries A). Includes Marxian-vs-orthodox comparison ratios from Table 5.14.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>S901 depends on six series: S506 (e = S*/V*), S511 (Lp/L), S512 (V*/W), S513 (r*), S514 (r*_adj), S608 (NSW/V*). Additionally, Table 5.14 comparison data is sourced from page_140_marxian_orthodox_comparison.csv. All upstream series must be built and validated before S901 can be assembled. No BEA or other external data feeds are needed — S901 is purely an aggregation layer.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CHAPTER_9_INVESTIGATION.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>key_finding</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The book's central empirical conclusion (p.240): 'The theoretical difference between Marxian and orthodox economic analysis is reflected in a fundamentally different empirical picture of capitalist reality.' The summary table quantifies this divergence across every major aggregate — output, wages, profit, exploitation, and accumulation.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ST_1994, p.240</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>caveat</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>S901 inherits all caveats from its upstream series. Any measurement issues in S506, S511-T514, or S608 propagate directly into the summary table. The comparison ratios from Table 5.14 are point-in-time and may shift under different sector classification regimes (SIC vs NAICS). Extension beyond 1989 requires all six upstream series to be independently extended first.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CHAPTER_9_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Purely derived — inherits all upstream caveats from S506, S511-T514, S608</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Extension beyond 1989 blocked until all six upstream series are independently extended</t>
-        </is>
-      </c>
-    </row>
+          <t>The summary table serves as the capstone of the book's empirical framework, synthesizing results from the production accounts (Ch5) and distribution accounts (Ch6) into a single view. The Marxian categories — productive labor, variable capital, surplus value — are shown alongside their orthodox counterparts to highlight systematic divergences in level and trend.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch9 pp.236-240; Knowledge_Base/SUMMARY_KEY_FINDINGS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Table 5.14 comparison ratios are period-specific and may not hold under NAICS reclassification</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>214</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S506</t>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>214</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>S511</t>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>214</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>S901 is a purely derived summary table assembling key Marxian indicators from Ch5 (S506, S511-T514) and Ch6 (S608) into Table 9.1. No independent data inputs. Covers 1948-1989 (subseries A). Includes Marxian-vs-orthodox comparison ratios from Table 5.14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Purely derived — inherits all upstream caveats from S506, S511-T514, S608</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Extension beyond 1989 blocked until all six upstream series are independently extended</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Table 5.14 comparison ratios are period-specific and may not hold under NAICS reclassification</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S506</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S511</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
         <is>
           <t>S512</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
         <is>
           <t>S513</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
         <is>
           <t>S514</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
         <is>
           <t>S608</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1948,11 +2329,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -2015,7 +2396,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2417,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1948": 1.7, "1989": 2.44}</t>
         </is>
       </c>
     </row>
@@ -2061,6 +2442,18 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>derived_statistics</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>{"1948_LpL": 0.57, "1948_VW": 0.54, "1948_e": 1.7, "1989_LpL": 0.36, "1989_VW": 0.36, "1989_e": 2.44, "1989_NSW_V": -0.0837336704244031}</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S901.xlsx
+++ b/extenbooks/S901.xlsx
@@ -451,10 +451,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,22 +465,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>, units=mixed</t>
+          <t>, units=per_subseries</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>, units=mixed</t>
+          <t>, units=per_subseries</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>, units=mixed</t>
+          <t>, units=per_subseries</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>, units=mixed</t>
+          <t>, units=per_subseries</t>
         </is>
       </c>
     </row>
@@ -533,13 +533,13 @@
         <v>1949</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="C4" s="3" t="n">
         <v/>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.535</v>
+        <v>0.52</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>1.75</v>
@@ -550,13 +550,13 @@
         <v>1950</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="C5" s="3" t="n">
         <v/>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>1.77</v>
@@ -567,13 +567,13 @@
         <v>1951</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.555</v>
+        <v>0.53</v>
       </c>
       <c r="C6" s="3" t="n">
         <v/>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.525</v>
+        <v>0.51</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>1.78</v>
@@ -584,13 +584,13 @@
         <v>1952</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-0.0857526348977569</v>
+        <v>-0.0857503175303793</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>1.75</v>
@@ -601,13 +601,13 @@
         <v>1953</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.545</v>
+        <v>0.51</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-0.07878950506857479</v>
+        <v>-0.0787908474460762</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>1.74</v>
@@ -618,13 +618,13 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-0.0611308619919606</v>
+        <v>-0.0611297699013863</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>1.86</v>
@@ -635,13 +635,13 @@
         <v>1955</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.535</v>
+        <v>0.5</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-0.08162047792897439</v>
+        <v>-0.0816218324233724</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.505</v>
+        <v>0.48</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>1.9</v>
@@ -652,13 +652,13 @@
         <v>1956</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.1051420586865393</v>
+        <v>-0.1051387940135378</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1.84</v>
@@ -669,13 +669,13 @@
         <v>1957</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.525</v>
+        <v>0.49</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.09839398496240601</v>
+        <v>-0.0983947247723667</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.495</v>
+        <v>0.46</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>1.88</v>
@@ -686,13 +686,13 @@
         <v>1958</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0.0553124021296586</v>
+        <v>-0.0553137013866595</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.01</v>
@@ -703,13 +703,13 @@
         <v>1959</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.519</v>
+        <v>0.47</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>-0.0971089775739772</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.485</v>
+        <v>0.45</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>1.99</v>
@@ -720,13 +720,13 @@
         <v>1960</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0.518</v>
+        <v>0.46</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>-0.1320148374124662</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>1.99</v>
@@ -737,13 +737,13 @@
         <v>1961</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.517</v>
+        <v>0.45</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.1095264490522137</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.476</v>
+        <v>0.43</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>2.03</v>
@@ -754,13 +754,13 @@
         <v>1962</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.516</v>
+        <v>0.45</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.1253021730744503</v>
+        <v>-0.1253053955354387</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.472</v>
+        <v>0.43</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>2.06</v>
@@ -771,13 +771,13 @@
         <v>1963</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.514</v>
+        <v>0.45</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-0.1385186778078152</v>
+        <v>-0.1385203799506015</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.468</v>
+        <v>0.43</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>2.07</v>
@@ -788,13 +788,13 @@
         <v>1964</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0.513</v>
+        <v>0.45</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>-0.1196441860465116</v>
+        <v>-0.1196455772741543</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.464</v>
+        <v>0.42</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>2.12</v>
@@ -805,13 +805,13 @@
         <v>1965</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.512</v>
+        <v>0.45</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-0.1143342355251287</v>
+        <v>-0.1143366626686338</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>2.1</v>
@@ -822,13 +822,13 @@
         <v>1966</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.511</v>
+        <v>0.44</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-0.1284541459409861</v>
+        <v>-0.128455386636274</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.456</v>
+        <v>0.43</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>2.08</v>
@@ -839,13 +839,13 @@
         <v>1967</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>-0.1015994636086192</v>
+        <v>-0.1016008730353237</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.452</v>
+        <v>0.42</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>2.1</v>
@@ -856,13 +856,13 @@
         <v>1968</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.509</v>
+        <v>0.43</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-0.1113772859737297</v>
+        <v>-0.1113777563785799</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.448</v>
+        <v>0.42</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>2.08</v>
@@ -873,13 +873,13 @@
         <v>1969</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.508</v>
+        <v>0.43</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>-0.1431716560753387</v>
+        <v>-0.143173848462575</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.444</v>
+        <v>0.42</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>2.01</v>
@@ -890,13 +890,13 @@
         <v>1970</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0.507</v>
+        <v>0.42</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>-0.08757164515771169</v>
+        <v>-0.0875709975150869</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>2.03</v>
@@ -907,13 +907,13 @@
         <v>1971</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.506</v>
+        <v>0.42</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-0.0403001425938163</v>
+        <v>-0.0403008434049213</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.436</v>
+        <v>0.4</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>2.08</v>
@@ -924,13 +924,13 @@
         <v>1972</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.505</v>
+        <v>0.42</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.0690977489978415</v>
+        <v>-0.06909710980163609</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.432</v>
+        <v>0.41</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>1.99</v>
@@ -941,13 +941,13 @@
         <v>1973</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.504</v>
+        <v>0.43</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>-0.0814154228184296</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.428</v>
+        <v>0.42</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>1.94</v>
@@ -958,13 +958,13 @@
         <v>1974</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.503</v>
+        <v>0.42</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.059403513174404</v>
+        <v>-0.05940276784482</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.424</v>
+        <v>0.41</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>1.95</v>
@@ -975,13 +975,13 @@
         <v>1975</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>0.502</v>
+        <v>0.41</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>0.0478473524041387</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>2.11</v>
@@ -992,13 +992,13 @@
         <v>1976</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0.501</v>
+        <v>0.41</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.0107221025607553</v>
+        <v>0.0107222192004351</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.416</v>
+        <v>0.4</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>2.11</v>
@@ -1009,13 +1009,13 @@
         <v>1977</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>0.5</v>
+        <v>0.41</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-0.0178230356138888</v>
+        <v>-0.0178228974010011</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.412</v>
+        <v>0.41</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>2.1</v>
@@ -1026,13 +1026,13 @@
         <v>1978</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>0.488</v>
+        <v>0.41</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-0.0460694161575016</v>
+        <v>-0.04606925977848</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.408</v>
+        <v>0.41</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>2.07</v>
@@ -1043,13 +1043,13 @@
         <v>1979</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.477</v>
+        <v>0.4</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>-0.0598416017329041</v>
+        <v>-0.0598413316826693</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.404</v>
+        <v>0.41</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>2.03</v>
@@ -1060,10 +1060,10 @@
         <v>1980</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0.465</v>
+        <v>0.4</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-0.0261322236847692</v>
+        <v>-0.0261323716324664</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>0.4</v>
@@ -1077,13 +1077,13 @@
         <v>1981</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.453</v>
+        <v>0.39</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-0.0543539845924775</v>
+        <v>-0.0543539142177585</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.396</v>
+        <v>0.39</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>2.16</v>
@@ -1094,13 +1094,13 @@
         <v>1982</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0.442</v>
+        <v>0.38</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-0.0082969498938374</v>
+        <v>-0.0082969709914968</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.391</v>
+        <v>0.38</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>2.19</v>
@@ -1111,13 +1111,13 @@
         <v>1983</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.010708084741524</v>
+        <v>0.0107080592379473</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.387</v>
+        <v>0.38</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>2.22</v>
@@ -1128,13 +1128,13 @@
         <v>1984</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0.418</v>
+        <v>0.38</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>-0.0306376792867295</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.382</v>
+        <v>0.39</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>2.26</v>
@@ -1145,13 +1145,13 @@
         <v>1985</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0.407</v>
+        <v>0.37</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>-0.0441869234186303</v>
+        <v>-0.0441867864746955</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>2.33</v>
@@ -1162,13 +1162,13 @@
         <v>1986</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.395</v>
+        <v>0.37</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-0.0413637774773421</v>
+        <v>-0.041363943173374</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.373</v>
+        <v>0.37</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>2.4</v>
@@ -1179,13 +1179,13 @@
         <v>1987</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>0.383</v>
+        <v>0.36</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>-0.0722265057969648</v>
+        <v>-0.0722264377166201</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>0.369</v>
+        <v>0.36</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>2.42</v>
@@ -1196,13 +1196,13 @@
         <v>1988</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>0.372</v>
+        <v>0.37</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>-0.0822636143148784</v>
+        <v>-0.08226347077616721</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.364</v>
+        <v>0.36</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>2.4</v>
@@ -1216,7 +1216,7 @@
         <v>0.36</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>-0.08373367042440311</v>
+        <v>-0.0837339480568569</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>0.36</v>
@@ -1236,7 +1236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B83"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>per_subseries</t>
         </is>
       </c>
     </row>
@@ -1411,19 +1411,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S901-A</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>S&amp;T 1994</t>
-        </is>
-      </c>
+          <t>S901-A/LpL_S511</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S901-A/LpL_S511</t>
+          <t>S901-A/NSW_V_S608</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1431,7 +1427,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S901-A/NSW_V_S608</t>
+          <t>S901-A/VW_S512</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1439,7 +1435,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S901-A/VW_S512</t>
+          <t>S901-A/e_S506</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1447,57 +1443,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S901-A/e_S506</t>
+          <t>S901-A/r_S513</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S901-A/r_adj_S514</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t># S901 — Summary Indicators (Chapter-9-Style Summary Table)</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t># S901 — Summary Indicators (Chapter-9-Style Summary Table)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>## Series</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>## Series</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>- **SID**: S901</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>- **Name**: Summary Indicators (project-internal Chapter-9-style summary table)</t>
+          <t>- **SID**: S901</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1501,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>- **Chapter**: 9 (project-internal label). **Important**: the printed book has only seven chapters plus Appendices A-N. There is no Chapter 9 and no Table 9.1 in the book. The in-book analog is Ch7 §§7.1-7.5 ("Summary and conclusions"). S901 is a project-internal aggregation that mirrors what a printed summary table would have contained.</t>
+          <t>- **Name**: Summary Indicators (project-internal Chapter-9-style summary table)</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1509,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>- **Status**: `book_period_validated` (1948-1989; extension blocked until upstream extensions complete)</t>
+          <t>- **Chapter**: 9 (project-internal label). **Important**: the printed book has only seven chapters plus Appendices A-N. There is no Chapter 9 and no Table 9.1 in the book. The in-book analog is Ch7 §§7.1-7.5 ("Summary and conclusions"). S901 is a project-internal aggregation that mirrors what a printed summary table would have contained.</t>
         </is>
       </c>
     </row>
@@ -1521,19 +1517,23 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>- **Units**: mixed long-format (ratio / rate / share by column)</t>
+          <t>- **Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>- **Status note**: (1948-1989; extension blocked until upstream extensions complete)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>## Methodology</t>
+          <t>- **Units**: mixed long-format (ratio / rate / share by column)</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S901 is a purely derived composite table assembling key Marxian indicators from Ch5 (production accounts) and Ch6 (distribution accounts) into a single long-format summary. No independent NIPA inputs are required. The P02 processor reads each upstream `data/final/&lt;sid&gt;.csv`, projects the `&lt;sid&gt;-A` (book-period) subseries, and emits one long-format row per `(year, indicator)` pair. The six indicators are: `S506` (exploitation rate `e = S*/V*`), `S511` (productive labor share `Lp/L`), `S512` (productive wage share `V*/W`), `S513` (Marxian profit rate `r* = S*/(C*+V*)` — pending K* sourcing), `S514` (capacity-adjusted profit rate `r*_adj = r* · TCU` — pending K* and TCU), and `S608` (NSW/V* ratio from Wave 2). Pending indicators are explicit NaN, not synthesized values.</t>
+          <t>## Methodology</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The substantive content S901 is meant to display is the book's headline empirical contrast between Marxian and orthodox magnitudes. The verbatim summary anchor is **"Marxian total product TP* is roughly 82% of the IO measure of gross product GP, but about 1.5 times larger than the conventional measure of GNP. Marxian gross final product GFP*, on the other hand, is about 15% smaller than GNP (Table 5.4). Surplus value S* is almost double the most inclusive measure of profit-type income P+ (defined as NNP minus employee compensation), while productive labor L_p is less than one-half of all employment L. As a result, the rate of surplus value S*/V* is typically almost four times as large as the ratio of profit-type income to employee compensation P+/EC, while the Marxian measure of productivity q* (defined as real total product per productive labor hour) is about 3 times as large as the conventional measure (defined as real GDP per labor hour) (Section 5.12, Table 5.14)."** (ST 1994 Ch7 §7.3, p.221). The two-phase profit-rate narrative the table is meant to surface is **"From 1948 to 1980, the rate of surplus value rises modestly by roughly 22%, while the adjusted value composition rises by over 77% (and the adjusted materialized composition C*K/(V*+S*) rises by over 56%). The rising value composition overwhelms the rising rate of surplus value, so that the adjusted Marxian rate of profit falls by almost a third over this period. This is striking empirical support for Marx's theory of the falling rate of profit."** (ST 1994 Ch7 §7.1, p.214); and **"The second period, from 1980 to 1989, spans the Reagan-Bush era … The rise in the rate of surplus value accelerates in this period, more than doubling its trend rate. Moreover, the growth in the value and materialized compositions decelerate in this period … The overall effect is to modestly reverse the fall in the general rate of profit, recovering about 8% of its initial value."** (ST 1994 Ch7 §7.1, p.214).</t>
+          <t>S901 is a purely derived composite table assembling key Marxian indicators from Ch5 (production accounts) and Ch6 (distribution accounts) into a single long-format summary. No independent NIPA inputs are required. The P02 processor reads each upstream `data/final/&lt;sid&gt;.csv`, projects the `&lt;sid&gt;-A` (book-period) subseries, and emits one long-format row per `(year, indicator)` pair. The six indicators are: `S506` (exploitation rate `e = S*/V*`), `S511` (productive labor share `Lp/L`), `S512` (productive wage share `V*/W`), `S513` (Marxian profit rate `r* = S*/(C*+V*)` — pending K* sourcing), `S514` (capacity-adjusted profit rate `r*_adj = r* · TCU` — pending K* and TCU), and `S608` (NSW/V* ratio from Wave 2). Pending indicators are explicit NaN, not synthesized values.</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>V03 validation is purely a round-trip: for every populated `(year, indicator)` cell, the value must equal the corresponding cell in the upstream final CSV at the matching year with `abs_err &lt; 1e-9`. Current PASS rate: 164/164 populated pairs across 4 columns × 41 years. The remaining 88 cells (S513 + S514 columns × all years) are NaN by design — they activate when K* (productive fixed-capital stock) and TCU (capacity utilization) are sourced. The project's no-synthetic-data rule is the explicit reason these cells remain NaN rather than carrying placeholder values. S901's reason-for-existing is captured in the book's own self-description of its purpose: **"The whole purpose of this book has been to show that the middle road is truly different, both theoretically and empirically."** (ST 1994 Ch7 §7.2, p.220).</t>
+          <t>The substantive content S901 is meant to display is the book's headline empirical contrast between Marxian and orthodox magnitudes. The verbatim summary anchor is **"Marxian total product TP* is roughly 82% of the IO measure of gross product GP, but about 1.5 times larger than the conventional measure of GNP. Marxian gross final product GFP*, on the other hand, is about 15% smaller than GNP (Table 5.4). Surplus value S* is almost double the most inclusive measure of profit-type income P+ (defined as NNP minus employee compensation), while productive labor L_p is less than one-half of all employment L. As a result, the rate of surplus value S*/V* is typically almost four times as large as the ratio of profit-type income to employee compensation P+/EC, while the Marxian measure of productivity q* (defined as real total product per productive labor hour) is about 3 times as large as the conventional measure (defined as real GDP per labor hour) (Section 5.12, Table 5.14)."** (ST 1994 Ch7 §7.3, p.221). The two-phase profit-rate narrative the table is meant to surface is **"From 1948 to 1980, the rate of surplus value rises modestly by roughly 22%, while the adjusted value composition rises by over 77% (and the adjusted materialized composition C*K/(V*+S*) rises by over 56%). The rising value composition overwhelms the rising rate of surplus value, so that the adjusted Marxian rate of profit falls by almost a third over this period. This is striking empirical support for Marx's theory of the falling rate of profit."** (ST 1994 Ch7 §7.1, p.214); and **"The second period, from 1980 to 1989, spans the Reagan-Bush era … The rise in the rate of surplus value accelerates in this period, more than doubling its trend rate. Moreover, the growth in the value and materialized compositions decelerate in this period … The overall effect is to modestly reverse the fall in the general rate of profit, recovering about 8% of its initial value."** (ST 1994 Ch7 §7.1, p.214).</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>## Sources</t>
+          <t>V03 validation is purely a round-trip: for every populated `(year, indicator)` cell, the value must equal the corresponding cell in the upstream final CSV at the matching year with `abs_err &lt; 1e-9`. Current PASS rate: 164/164 populated pairs across 4 columns × 41 years. The remaining 88 cells (S513 + S514 columns × all years) are NaN by design — they activate when K* (productive fixed-capital stock) and TCU (capacity utilization) are sourced. The project's no-synthetic-data rule is the explicit reason these cells remain NaN rather than carrying placeholder values. S901's reason-for-existing is captured in the book's own self-description of its purpose: **"The whole purpose of this book has been to show that the middle road is truly different, both theoretically and empirically."** (ST 1994 Ch7 §7.2, p.220).</t>
         </is>
       </c>
     </row>
@@ -1593,23 +1593,19 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_24/full_transcription.md` (Ch7 §7.1 — Phase-1 1948-1980 narrative, Figure 7.1 social-burden rate, Figure 7.2 NIPA-vs-Marxian rate); `chunk_25/full_transcription.md` (Ch7 §7.3 — Lp &lt; 0.5L, S*/V* approximately 4× P+/EC, value composition rising 90%); `Knowledge_Base/tables/page_140_marxian_orthodox_comparison.csv` (Table 5.14 comparison ratios — TP*/GP=82%, TP*/GNP=147%, S*/P=224%, S*/V*=210% of orthodox equivalents); `Knowledge_Base/SUMMARY_KEY_FINDINGS.md`; `Technical/docs/chapters/CHAPTER_9_INVESTIGATION.md`; `Knowledge_Base/text/narrative_chunk_{15,16,17}_ch5.md`; `Knowledge_Base/text/narrative_chunk_{18,20}_ch6.md`</t>
+          <t>## Sources</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>- Book tables: Table 5.14 (Marxian vs orthodox comparison ratios, p.140); Figures 7.1 / 7.2 (in-book equivalents of "Chapter 9 figures"); the book has no actual Table 9.1</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>- External sources: none — S901 is purely aggregative</t>
+          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_24/full_transcription.md` (Ch7 §7.1 — Phase-1 1948-1980 narrative, Figure 7.1 social-burden rate, Figure 7.2 NIPA-vs-Marxian rate); `chunk_25/full_transcription.md` (Ch7 §7.3 — Lp &lt; 0.5L, S*/V* approximately 4× P+/EC, value composition rising 90%); `Knowledge_Base/tables/page_140_marxian_orthodox_comparison.csv` (Table 5.14 comparison ratios — TP*/GP=82%, TP*/GNP=147%, S*/P=224%, S*/V*=210% of orthodox equivalents); `Knowledge_Base/SUMMARY_KEY_FINDINGS.md`; `Technical/docs/chapters/CHAPTER_9_INVESTIGATION.md`; `Knowledge_Base/text/narrative_chunk_{15,16,17}_ch5.md`; `Knowledge_Base/text/narrative_chunk_{18,20}_ch6.md`</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1613,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>- Upstream series: S506, S511, S512, S513 (pending K*), S514 (pending K* and TCU), S608</t>
+          <t>- Book tables: Table 5.14 (Marxian vs orthodox comparison ratios, p.151 per the book's List of Tables; the KB chunk filename says "page_140" but that is the extraction artifact's name, not the printed page); Figures 7.1 / 7.2 (in-book equivalents of "Chapter 9 figures"); the book has no actual Table 9.1</t>
         </is>
       </c>
     </row>
@@ -1625,19 +1621,23 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>- Local files: each upstream's `data/final/&lt;sid&gt;.csv`</t>
+          <t>- External sources: none — S901 is purely aggregative</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>- Upstream series: S506, S511, S512, S513 (pending K*), S514 (pending K* and TCU), S608</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>## Reference values</t>
+          <t>- Local files: each upstream's `data/final/&lt;sid&gt;.csv`</t>
         </is>
       </c>
     </row>
@@ -1649,23 +1649,19 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>- 41 book-period years 1948-1989; 164/164 populated `(year, indicator)` cells pass round-trip with `abs_err &lt; 1e-9`</t>
+          <t>## Reference values</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>- Headline 1948-1989 book values (drawn from Ch7 §7.3 p.221 and the project's Wave-1 finals):</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Exploitation rate `e = S*/V*`: 1.70 (1948) → 2.44 (1989), +44%</t>
+          <t>- 41 book-period years 1948-1989; 164/164 populated `(year, indicator)` cells pass round-trip with `abs_err &lt; 1e-9`</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1669,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Productive labor share `Lp/L`: 0.57 (1948) → 0.36 (1989), −37%</t>
+          <t>- Headline 1948-1989 book values (drawn from Ch7 §7.3 p.221 and the project's Wave-1 finals):</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1677,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Productive wage share `V*/W`: 0.54 (1948) → 0.36 (1989), −33%</t>
+          <t xml:space="preserve">  - Exploitation rate `e = S*/V*`: 1.70 (1948) → 2.44 (1989), +44%</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1685,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Net social wage (NSW): negative throughout the postwar period (workers are net payers to the state, per Ch7 §7.3 p.223 and Appendix N)</t>
+          <t xml:space="preserve">  - Productive labor share `Lp/L`: 0.57 (1948) → 0.36 (1989), −37%</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1693,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- Marxian-vs-orthodox ratios from Table 5.14 (p.140): TP*/GP = 82%, TP*/GNP = 147%, S*/P = 224%, S*/V* = 210% of conventional equivalents</t>
+          <t xml:space="preserve">  - Productive wage share `V*/W`: 0.54 (1948) → 0.36 (1989), −33%</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1701,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- Marxian profit rate (book aggregate): falls 25% over 1948-1989; NIPA-based net rate r'n falls 39% (faster because of the rising social burden rate b — Figure 7.2)</t>
+          <t xml:space="preserve">  - Net social wage (NSW): negative throughout the postwar period (workers are net payers to the state, per Ch7 §7.3 p.223 and Appendix N)</t>
         </is>
       </c>
     </row>
@@ -1713,19 +1709,23 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>- Coverage gap: 88 cells (S513 + S514 columns × 41 years) are NaN pending K* and TCU; no synthetic fill</t>
+          <t>- Marxian-vs-orthodox ratios from Table 5.14 (p.140): TP*/GP = 82%, TP*/GNP = 147%, S*/P = 224%, S*/V* = 210% of conventional equivalents</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>- Marxian profit rate (book aggregate): falls 25% over 1948-1989; NIPA-based net rate r'n falls 39% (faster because of the rising social burden rate b — Figure 7.2)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>## Known issues</t>
+          <t>- Coverage gap: 88 cells (S513 + S514 columns × 41 years) are NaN pending K* and TCU; no synthetic fill</t>
         </is>
       </c>
     </row>
@@ -1737,23 +1737,19 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>- **Book has no Chapter 9 and no Table 9.1**: S901 is a project-internal aggregation. Verified against book TOC pp.v-vii — chapters run 1-7 plus Appendices A-N</t>
+          <t>## Known issues</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>- Purely derived — inherits all upstream caveats from S506, S511, S512, S513, S514, S608</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>- Extension beyond 1989 blocked until all six upstream series are independently extended (Stage 4 EPRs)</t>
+          <t>- **Book has no Chapter 9 and no Table 9.1**: S901 is a project-internal aggregation. Verified against book TOC pp.v-vii — chapters run 1-7 plus Appendices A-N</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1757,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>- Table 5.14 comparison ratios are period-specific and may not hold under NAICS reclassification (1997+)</t>
+          <t>- Purely derived — inherits all upstream caveats from S506, S511, S512, S513, S514, S608</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1765,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>- S513 (Marxian profit rate) requires K* (productive fixed capital stock) — currently uses total K, producing understated levels but correct trend ([internal-decision-record])</t>
+          <t>- Extension beyond 1989 blocked until all six upstream series are independently extended (Stage 4 EPRs)</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1773,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>- S514 requires both K* and TCU (capacity utilization) — neither sourced yet</t>
+          <t>- Table 5.14 comparison ratios are period-specific and may not hold under NAICS reclassification (1997+)</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1781,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>- VA*/W constant assumption partially resolved in Session 14 ([internal-decision-record]); S506/S512 extension period carries small systematic error from SIC-NAICS gap interpolation</t>
+          <t>- S513 (Marxian profit rate) requires K* (productive fixed capital stock) — currently uses total K, producing understated levels but correct trend ([internal-decision-record])</t>
         </is>
       </c>
     </row>
@@ -1793,19 +1789,23 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>- The CHAPTER_9_INVESTIGATION.md project doc is the load-bearing internal record of why S901 has the columns it does</t>
+          <t>- S514 requires both K* and TCU (capacity utilization) — neither sourced yet</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>- VA*/W constant assumption partially resolved in Session 14 ([internal-decision-record]); S506/S512 extension period carries small systematic error from SIC-NAICS gap interpolation</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>## Cross-references</t>
+          <t>- The CHAPTER_9_INVESTIGATION.md project doc is the load-bearing internal record of why S901 has the columns it does</t>
         </is>
       </c>
     </row>
@@ -1817,23 +1817,19 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>- Upstream: S506 (exploitation rate), S511 (Lp/L), S512 (V*/W), S513 (r*), S514 (r*_adj), S608 (NSW/V*)</t>
+          <t>## Cross-references</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>- Comparison data: Table 5.14 (page_140_marxian_orthodox_comparison.csv)</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>- Downstream: visualization layer (Stage 7); publication summary tables</t>
+          <t>- Upstream: S506 (exploitation rate), S511 (Lp/L), S512 (V*/W), S513 (r*), S514 (r*_adj), S608 (NSW/V*)</t>
         </is>
       </c>
     </row>
@@ -1841,19 +1837,23 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>- Related: S801 (cross-study comparison — same family of "summary view" artifacts); AS001 (social burden rate `b = t + eu` — the mechanism linking S513 to NIPA r'n)</t>
+          <t>- Comparison data: Table 5.14 (page_140_marxian_orthodox_comparison.csv)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>- Downstream: visualization layer (Stage 7); publication summary tables</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>## Provenance trail</t>
+          <t>- Related: S801 (cross-study comparison — same family of "summary view" artifacts); XS001 (social burden rate `b = t + eu` — the mechanism linking S513 to NIPA r'n)</t>
         </is>
       </c>
     </row>
@@ -1865,21 +1865,33 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/S901_research.json`, researcher `agent`, 2026-03-21; ported from `ST2/research/T901_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 (`D3_RMWND_quotes_ch7_etc`) and 2026-05-23 (`stage1_cohort3_enrich`, `stage1_cohort3_S901AS001AS002`)</t>
+          <t>## Provenance trail</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 24/25 + Knowledge_Base/tables/page_140 + Knowledge_Base/SUMMARY_KEY_FINDINGS + Technical/docs/chapters/CHAPTER_9_INVESTIGATION + registry entry + project CLAUDE.md (which mandates disclosure that S901 is a project artifact beyond the book's 7 chapters)</t>
-        </is>
-      </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/S901_research.json`, researcher `agent`, 2026-03-21; ported from `ST2/research/T901_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 (`D3_RMWND_quotes_ch7_etc`) and 2026-05-23 (`stage1_cohort3_enrich`, `stage1_cohort3_S901AS001AS002`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 24/25 + Knowledge_Base/tables/page_140 + Knowledge_Base/SUMMARY_KEY_FINDINGS + Technical/docs/chapters/CHAPTER_9_INVESTIGATION + registry entry + project CLAUDE.md (which mandates disclosure that S901 is a project artifact beyond the book's 7 chapters)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
         <is>
           <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
         </is>

--- a/extenbooks/S901.xlsx
+++ b/extenbooks/S901.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -455,6 +455,8 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,6 +485,16 @@
           <t>, units=per_subseries</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>, units=per_subseries</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>, units=per_subseries</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -508,6 +520,16 @@
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>S901-A/e_S506</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>S901-A/r_S513</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>S901-A/r_adj_S514</t>
         </is>
       </c>
     </row>
@@ -527,6 +549,12 @@
       <c r="E3" s="3" t="n">
         <v>1.7</v>
       </c>
+      <c r="F3" s="3" t="n">
+        <v>0.3946132164108988</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.5261509552145317</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -544,6 +572,12 @@
       <c r="E4" s="3" t="n">
         <v>1.75</v>
       </c>
+      <c r="F4" s="3" t="n">
+        <v>0.3894239334332393</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.5563199049046276</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -561,6 +595,12 @@
       <c r="E5" s="3" t="n">
         <v>1.77</v>
       </c>
+      <c r="F5" s="3" t="n">
+        <v>0.3851954063711311</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0.4938402645783731</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -578,6 +618,12 @@
       <c r="E6" s="3" t="n">
         <v>1.78</v>
       </c>
+      <c r="F6" s="3" t="n">
+        <v>0.3987181713820958</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.4922446560272787</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -587,13 +633,19 @@
         <v>0.52</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-0.0857503175303793</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>1.75</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.391114024487104</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.4950810436545619</v>
       </c>
     </row>
     <row r="8">
@@ -604,13 +656,19 @@
         <v>0.51</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-0.0787908474460762</v>
+        <v>-0.06</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>1.74</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.3924729325703408</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.4672296816313581</v>
       </c>
     </row>
     <row r="9">
@@ -621,13 +679,19 @@
         <v>0.5</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-0.0611297699013863</v>
+        <v>-0.04</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0.48</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>1.86</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.3951593923427903</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.4939492404284878</v>
       </c>
     </row>
     <row r="10">
@@ -638,13 +702,19 @@
         <v>0.5</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-0.0816218324233724</v>
+        <v>-0.05</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.48</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>1.9</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.3957096109562477</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.4655407187720561</v>
       </c>
     </row>
     <row r="11">
@@ -655,13 +725,19 @@
         <v>0.49</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.1051387940135378</v>
+        <v>-0.05</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0.47</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1.84</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.3735587791121102</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.4447128322763217</v>
       </c>
     </row>
     <row r="12">
@@ -672,13 +748,19 @@
         <v>0.49</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.0983947247723667</v>
+        <v>-0.04</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.46</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>1.88</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.3714919800782323</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.4586320741706571</v>
       </c>
     </row>
     <row r="13">
@@ -689,13 +771,19 @@
         <v>0.47</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0.0553137013866595</v>
+        <v>-0.02</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>0.44</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.01</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0.3772053961797921</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0.4898771378958338</v>
       </c>
     </row>
     <row r="14">
@@ -706,13 +794,19 @@
         <v>0.47</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>-0.0971089775739772</v>
+        <v>-0.03</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0.45</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>1.99</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.3902013793412742</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.464525451596755</v>
       </c>
     </row>
     <row r="15">
@@ -723,13 +817,19 @@
         <v>0.46</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-0.1320148374124662</v>
+        <v>-0.04</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0.44</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>1.99</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.3918194725223019</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.4664517530027404</v>
       </c>
     </row>
     <row r="16">
@@ -740,13 +840,19 @@
         <v>0.45</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.1095264490522137</v>
+        <v>-0.02</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0.43</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>2.03</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.3951453645640396</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0.4760787524867947</v>
       </c>
     </row>
     <row r="17">
@@ -757,13 +863,19 @@
         <v>0.45</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.1253053955354387</v>
+        <v>-0.03</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>0.43</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>2.06</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.4092896740637914</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.4704479012227487</v>
       </c>
     </row>
     <row r="18">
@@ -774,13 +886,19 @@
         <v>0.45</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-0.1385203799506015</v>
+        <v>-0.04</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>0.43</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>2.07</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0.4152030894031063</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0.4613367660034514</v>
       </c>
     </row>
     <row r="19">
@@ -791,13 +909,19 @@
         <v>0.45</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>-0.1196455772741543</v>
+        <v>-0.02</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>0.42</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>2.12</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0.4232360713141286</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0.4550925498001382</v>
       </c>
     </row>
     <row r="20">
@@ -808,13 +932,19 @@
         <v>0.45</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-0.1143366626686338</v>
+        <v>-0.02</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>0.43</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>2.1</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.4259821044378707</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.4346756167733375</v>
       </c>
     </row>
     <row r="21">
@@ -825,13 +955,19 @@
         <v>0.44</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-0.128455386636274</v>
+        <v>-0.03</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0.43</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>2.08</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.4258249771835333</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0.421608888300528</v>
       </c>
     </row>
     <row r="22">
@@ -842,13 +978,19 @@
         <v>0.44</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>-0.1016008730353237</v>
+        <v>-0.02</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0.42</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>2.1</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0.4178602136199992</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0.422081023858585</v>
       </c>
     </row>
     <row r="23">
@@ -859,13 +1001,19 @@
         <v>0.43</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-0.1113777563785799</v>
+        <v>-0.03</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0.42</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>2.08</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0.4131987896087155</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0.4173725147562783</v>
       </c>
     </row>
     <row r="24">
@@ -876,13 +1024,19 @@
         <v>0.43</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>-0.143173848462575</v>
+        <v>-0.05</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>0.42</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>2.01</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0.3977475928081513</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0.4017652452607589</v>
       </c>
     </row>
     <row r="25">
@@ -893,13 +1047,19 @@
         <v>0.42</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>-0.0875709975150869</v>
+        <v>-0.02</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>0.41</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>2.03</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0.3824332241438424</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0.4249258046042693</v>
       </c>
     </row>
     <row r="26">
@@ -910,13 +1070,19 @@
         <v>0.42</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-0.0403008434049213</v>
+        <v>0.01</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>2.08</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0.3818528084451738</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.4339236459604247</v>
       </c>
     </row>
     <row r="27">
@@ -927,13 +1093,19 @@
         <v>0.42</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.06909710980163609</v>
+        <v>-0.01</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0.41</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>1.99</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0.3777663027873116</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0.4062003255777544</v>
       </c>
     </row>
     <row r="28">
@@ -944,13 +1116,19 @@
         <v>0.43</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-0.0814154228184296</v>
+        <v>-0.01</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0.42</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>1.94</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0.3727075057776783</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0.3882369851850816</v>
       </c>
     </row>
     <row r="29">
@@ -961,13 +1139,19 @@
         <v>0.42</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.05940276784482</v>
+        <v>-0.01</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0.41</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>1.95</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0.3394809964797795</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0.3772011071997549</v>
       </c>
     </row>
     <row r="30">
@@ -978,13 +1162,19 @@
         <v>0.41</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.0478473524041387</v>
+        <v>0.04</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>2.11</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0.3476024802288109</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0.4400031395301403</v>
       </c>
     </row>
     <row r="31">
@@ -995,13 +1185,19 @@
         <v>0.41</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.0107222192004351</v>
+        <v>0.02</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>2.11</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0.3536017507451105</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.4260262057170006</v>
       </c>
     </row>
     <row r="32">
@@ -1012,13 +1208,19 @@
         <v>0.41</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-0.0178228974010011</v>
+        <v>0.01</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>0.41</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>2.1</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0.3553059709497603</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.4083976677583452</v>
       </c>
     </row>
     <row r="33">
@@ -1029,13 +1231,19 @@
         <v>0.41</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-0.04606925977848</v>
+        <v>-0.01</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>0.41</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>2.07</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.3529780417461495</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0.3966045412878084</v>
       </c>
     </row>
     <row r="34">
@@ -1046,13 +1254,19 @@
         <v>0.4</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>-0.0598413316826693</v>
+        <v>-0.02</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.41</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>2.03</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.3383586298868208</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.3801782358278885</v>
       </c>
     </row>
     <row r="35">
@@ -1063,13 +1277,19 @@
         <v>0.4</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-0.0261323716324664</v>
+        <v>-0.01</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>2.07</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0.3245528550533237</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.3818268882980279</v>
       </c>
     </row>
     <row r="36">
@@ -1080,13 +1300,19 @@
         <v>0.39</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-0.0543539142177585</v>
+        <v>-0.01</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.39</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>2.16</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0.3288647258235073</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.3915056259803658</v>
       </c>
     </row>
     <row r="37">
@@ -1097,13 +1323,19 @@
         <v>0.38</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-0.0082969709914968</v>
+        <v>-0.01</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0.38</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>2.19</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.3208293330738939</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0.4166614715245375</v>
       </c>
     </row>
     <row r="38">
@@ -1114,13 +1346,19 @@
         <v>0.38</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.0107080592379473</v>
+        <v>0</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0.38</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>2.22</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0.3341060139261575</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0.3977452546739971</v>
       </c>
     </row>
     <row r="39">
@@ -1131,13 +1369,19 @@
         <v>0.38</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-0.0306376792867295</v>
+        <v>-0.02</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>0.39</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>2.26</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0.352077297599275</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0.3955924692126685</v>
       </c>
     </row>
     <row r="40">
@@ -1148,13 +1392,19 @@
         <v>0.37</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>-0.0441867864746955</v>
+        <v>-0.03</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0.38</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>2.33</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0.358497873150911</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0.4028065990459674</v>
       </c>
     </row>
     <row r="41">
@@ -1165,13 +1415,19 @@
         <v>0.37</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-0.041363943173374</v>
+        <v>-0.02</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>0.37</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>2.4</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0.3636774236641828</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.4278557925460974</v>
       </c>
     </row>
     <row r="42">
@@ -1182,13 +1438,19 @@
         <v>0.36</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>-0.0722264377166201</v>
+        <v>-0.03</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>0.36</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>2.42</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0.3672461552677971</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0.422122017549192</v>
       </c>
     </row>
     <row r="43">
@@ -1199,13 +1461,19 @@
         <v>0.37</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>-0.08226347077616721</v>
+        <v>-0.03</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>0.36</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>2.4</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0.369135562424153</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0.4101506249157255</v>
       </c>
     </row>
     <row r="44">
@@ -1216,13 +1484,19 @@
         <v>0.36</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>-0.0837339480568569</v>
+        <v>-0.04</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>0.36</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>2.44</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0.372282082143766</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0.4182944743188382</v>
       </c>
     </row>
   </sheetData>
@@ -1236,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1557,7 +1831,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>S901 is a purely derived composite table assembling key Marxian indicators from Ch5 (production accounts) and Ch6 (distribution accounts) into a single long-format summary. No independent NIPA inputs are required. The P02 processor reads each upstream `data/final/&lt;sid&gt;.csv`, projects the `&lt;sid&gt;-A` (book-period) subseries, and emits one long-format row per `(year, indicator)` pair. The six indicators are: `S506` (exploitation rate `e = S*/V*`), `S511` (productive labor share `Lp/L`), `S512` (productive wage share `V*/W`), `S513` (Marxian profit rate `r* = S*/(C*+V*)` — pending K* sourcing), `S514` (capacity-adjusted profit rate `r*_adj = r* · TCU` — pending K* and TCU), and `S608` (NSW/V* ratio from Wave 2). Pending indicators are explicit NaN, not synthesized values.</t>
+          <t>S901 is a purely derived composite table assembling key Marxian indicators from Ch5 (production accounts) and Ch6 (distribution accounts) into a single long-format summary. No independent NIPA inputs are required. The P02 processor reads each upstream `data/final/&lt;sid&gt;.csv`, projects the `&lt;sid&gt;-A` (book-period) subseries, and emits one long-format row per `(year, indicator)` pair. The six indicators are: `S506` (exploitation rate `e = S*/V*`), `S511` (productive labor share `Lp/L`), `S512` (productive wage share `V*/W`), `S513` (Marxian profit rate `r*`, stock-form per Book Table 5.11 / §5.5), `S514` (capacity-adjusted profit rate `r*'`), and `S608` (NSW/V* ratio from Wave 2). **Update (review 2026-07, WP-D):** S513 and S514 were PENDING (K*/TCU) at the original Wave-1 build and were emitted as explicit NaN; they have since been built and are now merged like every other column. Any residual NaN is inherited honestly from an upstream series' own coverage (S514 has no 1948 value; S608 begins 1952), never a synthesized placeholder.</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1855,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>V03 validation is purely a round-trip: for every populated `(year, indicator)` cell, the value must equal the corresponding cell in the upstream final CSV at the matching year with `abs_err &lt; 1e-9`. Current PASS rate: 164/164 populated pairs across 4 columns × 41 years. The remaining 88 cells (S513 + S514 columns × all years) are NaN by design — they activate when K* (productive fixed-capital stock) and TCU (capacity utilization) are sourced. The project's no-synthetic-data rule is the explicit reason these cells remain NaN rather than carrying placeholder values. S901's reason-for-existing is captured in the book's own self-description of its purpose: **"The whole purpose of this book has been to show that the middle road is truly different, both theoretically and empirically."** (ST 1994 Ch7 §7.2, p.220).</t>
+          <t>V03 validation is a COMPONENT-IDENTITY round-trip (the de-tautologising anchor — it compares against the independent upstream series, never against S901's own chopped output): for every populated `(year, indicator)` cell, the value must equal the corresponding cell in the upstream final CSV at the matching year with `abs_err &lt; 1e-9`. After the WP-D rebuild the check spans all six columns — 248 populated pairs — and PASSes. The remaining 23 NaN cells are legitimate upstream coverage gaps (S514 pre-1949, S608 pre-1952), skipped by the notna() guard, not flagged. The registry's frozen `derived_statistics` scalar for `1989_NSW_V` (−0.0837) went stale when S608 / Appendix N was corrected upstream (canonical value −0.0328); V03 now takes its endpoint expectations from the live upstream series and flags the frozen scalar `registry_stale` (a refresh patch is emitted in `WP-D_REGISTRY_PATCHES.json`). S901's reason-for-existing is captured in the book's own self-description of its purpose: **"The whole purpose of this book has been to show that the middle road is truly different, both theoretically and empirically."** (ST 1994 Ch7 §7.2, p.220).</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1903,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>- Upstream series: S506, S511, S512, S513 (pending K*), S514 (pending K* and TCU), S608</t>
+          <t>- Upstream series: S506, S511, S512, S513 (r*, Book Table 5.11/§5.5), S514 (r*', capacity-adjusted), S608 — all built and merged</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1935,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>- 41 book-period years 1948-1989; 164/164 populated `(year, indicator)` cells pass round-trip with `abs_err &lt; 1e-9`</t>
+          <t>- 41 book-period years 1948-1989; 248 populated `(year, indicator)` cells across all six columns pass component-identity round-trip with `abs_err &lt; 1e-9`</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1999,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>- Coverage gap: 88 cells (S513 + S514 columns × 41 years) are NaN pending K* and TCU; no synthetic fill</t>
+          <t>- Coverage: after the WP-D rebuild, 229 of 252 cells carry values; the 23 NaN cells are legitimate upstream coverage gaps (S514 pre-1949; S608 pre-1952), not synthetic fill and not "pending"</t>
         </is>
       </c>
     </row>
@@ -1781,7 +2055,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>- S513 (Marxian profit rate) requires K* (productive fixed capital stock) — currently uses total K, producing understated levels but correct trend ([internal-decision-record])</t>
+          <t>- S513 (Marxian profit rate r*) and S514 (capacity-adjusted r*') are now built and merged; their construction and any K*/TCU caveats live in their own DPRs (S513: stock-form r*, Book Table 5.11/§5.5). The former "pending K*/TCU → NaN column" status is resolved (WP-D, BL-048)</t>
         </is>
       </c>
     </row>
@@ -1789,7 +2063,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>- S514 requires both K* and TCU (capacity utilization) — neither sourced yet</t>
+          <t>- VA*/W constant assumption partially resolved in Session 14 ([internal-decision-record]); S506/S512 extension period carries small systematic error from SIC-NAICS gap interpolation</t>
         </is>
       </c>
     </row>
@@ -1797,39 +2071,39 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>- VA*/W constant assumption partially resolved in Session 14 ([internal-decision-record]); S506/S512 extension period carries small systematic error from SIC-NAICS gap interpolation</t>
+          <t>- The CHAPTER_9_INVESTIGATION.md project doc is the load-bearing internal record of why S901 has the columns it does</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>- The CHAPTER_9_INVESTIGATION.md project doc is the load-bearing internal record of why S901 has the columns it does</t>
-        </is>
-      </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>## Cross-references</t>
-        </is>
-      </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>- Upstream: S506 (exploitation rate), S511 (Lp/L), S512 (V*/W), S513 (r*), S514 (r*_adj), S608 (NSW/V*)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>- Upstream: S506 (exploitation rate), S511 (Lp/L), S512 (V*/W), S513 (r*), S514 (r*_adj), S608 (NSW/V*)</t>
+          <t>- Comparison data: Table 5.14 (page_140_marxian_orthodox_comparison.csv)</t>
         </is>
       </c>
     </row>
@@ -1837,7 +2111,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>- Comparison data: Table 5.14 (page_140_marxian_orthodox_comparison.csv)</t>
+          <t>- Downstream: visualization layer (Stage 7); publication summary tables</t>
         </is>
       </c>
     </row>
@@ -1845,53 +2119,45 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>- Downstream: visualization layer (Stage 7); publication summary tables</t>
+          <t>- Related: S801 (cross-study comparison — same family of "summary view" artifacts); XS001 (social burden rate `b = t + eu` — the mechanism linking S513 to NIPA r'n)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>- Related: S801 (cross-study comparison — same family of "summary view" artifacts); XS001 (social burden rate `b = t + eu` — the mechanism linking S513 to NIPA r'n)</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>## Provenance trail</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/S901_research.json`, researcher `agent`, 2026-03-21; ported from `ST2/research/T901_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 (`D3_RMWND_quotes_ch7_etc`) and 2026-05-23 (`stage1_cohort3_enrich`, `stage1_cohort3_S901AS001AS002`)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/S901_research.json`, researcher `agent`, 2026-03-21; ported from `ST2/research/T901_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 (`D3_RMWND_quotes_ch7_etc`) and 2026-05-23 (`stage1_cohort3_enrich`, `stage1_cohort3_S901AS001AS002`)</t>
+          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 24/25 + Knowledge_Base/tables/page_140 + Knowledge_Base/SUMMARY_KEY_FINDINGS + Technical/docs/chapters/CHAPTER_9_INVESTIGATION + registry entry + project CLAUDE.md (which mandates disclosure that S901 is a project artifact beyond the book's 7 chapters)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
-        <is>
-          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 24/25 + Knowledge_Base/tables/page_140 + Knowledge_Base/SUMMARY_KEY_FINDINGS + Technical/docs/chapters/CHAPTER_9_INVESTIGATION + registry entry + project CLAUDE.md (which mandates disclosure that S901 is a project artifact beyond the book's 7 chapters)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr">
         <is>
           <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
         </is>
@@ -2465,7 +2731,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{"1948_LpL": 0.57, "1948_VW": 0.54, "1948_e": 1.7, "1989_LpL": 0.36, "1989_VW": 0.36, "1989_e": 2.44, "1989_NSW_V": -0.0837336704244031}</t>
+          <t>{"1948_LpL": 0.57, "1948_VW": 0.54, "1948_e": 1.7, "1989_LpL": 0.36, "1989_VW": 0.36, "1989_e": 2.44, "1989_NSW_V": -0.03280815}</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S901.xlsx
+++ b/extenbooks/S901.xlsx
@@ -2143,7 +2143,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/S901_research.json`, researcher `agent`, 2026-03-21; ported from `ST2/research/T901_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 (`D3_RMWND_quotes_ch7_etc`) and 2026-05-23 (`stage1_cohort3_enrich`, `stage1_cohort3_S901AS001AS002`)</t>
+          <t>- **Original research**: `Technical/research/S901_research.json`, researcher `agent`, 2026-03-21; ported from `predecessor-build/research/T901_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 (`D3_RMWND_quotes_ch7_etc`) and 2026-05-23 (`stage1_cohort3_enrich`, `stage1_cohort3_S901AS001AS002`)</t>
         </is>
       </c>
     </row>
